--- a/survey_templates/049_tone_evaluation_form--survey_templates.xlsx
+++ b/survey_templates/049_tone_evaluation_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tone Evaluation Form</t>
+          <t>What is your overall impression of the text?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Select the Tone of the text</t>
+          <t>Select all the tones that you feel are present in the text.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,87 +566,87 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>tone_1</t>
+          <t>page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tone</t>
+          <t>How would you rate the text's tone?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>tone_2</t>
+          <t>page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tone</t>
+          <t>What are your overall feedback on the text?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>tone_3</t>
+          <t>page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tone</t>
+          <t>What do you think about the text's content?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page_3</t>
+          <t>page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tone Evaluation Form</t>
+          <t>How does the text's tone make you feel?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,110 +658,110 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>feedback_1</t>
+          <t>page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Do you have any additional feedback about the text?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>feedback_2</t>
+          <t>page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Is the text's tone consistent with the content?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>feedback_3</t>
+          <t>page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>How would you rate the text's tone if you were to read it again?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>page_4</t>
+          <t>page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tone Evaluation Form</t>
+          <t>Would you recommend the text to a friend?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>tone_4</t>
+          <t>page_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tone</t>
+          <t>Why or why not?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,110 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>tone_5</t>
+          <t>page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tone</t>
+          <t>How would you rate the text overall?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>tone_6</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Tone</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>feedback_3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Feedback</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>feedback_4</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Feedback</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -891,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -919,544 +827,612 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>1._very_positive</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1. Very positive</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>2._positive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2. Positive</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tone_1_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3._neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3. Neutral</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tone_1_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4._negative</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4. Negative</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tone_1_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5._very_negative</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5. Very negative</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tone_1_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1._friendly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1. Friendly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tone_1_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2._formal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2. Formal</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tone_2_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3._critical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3. Critical</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tone_2_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4._positive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4. Positive</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tone_2_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5._negative</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5. Negative</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tone_2_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6._very_positive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6. Very positive</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tone_2_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7._very_negative</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7. Very negative</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tone_3_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1._very_positive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1. Very positive</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tone_3_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2._positive</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2. Positive</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tone_3_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3._neutral</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3. Neutral</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tone_3_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4._negative</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4. Negative</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tone_3_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5._very_negative</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5. Very negative</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tone_4_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1._very_positive</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1. Very positive</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tone_4_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2._positive</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2. Positive</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tone_4_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3._neutral</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3. Neutral</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tone_4_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4._negative</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4. Negative</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tone_4_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5._very_negative</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5. Very negative</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tone_5_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1._yes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1. Yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tone_5_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2._no</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2. No</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tone_5_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1._very_positive</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1. Very positive</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tone_5_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2._positive</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2. Positive</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tone_5_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3._neutral</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3. Neutral</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tone_6_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4._negative</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4. Negative</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tone_6_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5._very_negative</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5. Very negative</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tone_6_choices</t>
+          <t>page_10_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1._yes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1. Yes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tone_6_choices</t>
+          <t>page_10_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2._no</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2. No</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tone_6_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1._very_positive</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1. Very positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>page_12_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2._positive</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2. Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>page_12_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>3._neutral</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3. Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>page_12_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>4._negative</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>4. Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>page_12_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5._very_negative</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>5. Very negative</t>
         </is>
       </c>
     </row>
